--- a/news_daily/2026-10-06.xlsx
+++ b/news_daily/2026-10-06.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +534,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,6 +841,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -877,7 +901,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -887,13 +911,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -933,7 +961,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -946,7 +974,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f9554de6cc024f99baee66bbdba239ff</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>f21f7d93c3daa8a164f5c59a</t>
@@ -971,7 +1003,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1015,6 +1051,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1193,6 +1245,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1371,6 +1427,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1549,6 +1609,10 @@
       </c>
       <c r="BG5" s="4" t="inlineStr"/>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1727,6 +1791,10 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1897,184 +1965,216 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>BALL</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Ball Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Daniil Medvedev defaulted from China Open after striking spectator with ball - The Athletic</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>'-0.784</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeW81aUc3dERZMHZITHp0Zlg5OWZhb09IYUUwZTJfcTQ5Z3RYQ3BsU3dYeVJMbFZ0TDNWcEZ5d1NRVGgteXV0QW1OVDRQSE8tekh1QWFndXFON1NaYVI4em1DT2stQmZYQnRUNVZTM3p6MjBCOHRsMXdtYXZVUVd5Y19VZW44OFh3bEpIU3E1Mnk2ZUZDUDVjWF9pWmlmSEExQW5OdA?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>The New York Times</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>eab9231675914654aee8756a674f46c0</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>86474f46fbfe7c4f1e4a0e19</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>be5b6c35dfdad987def51679</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>BALL-DEFAULT-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>'-0.784</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeW81aUc3dERZMHZITHp0Zlg5OWZhb09IYUUwZTJfcTQ5Z3RYQ3BsU3dYeVJMbFZ0TDNWcEZ5d1NRVGgteXV0QW1OVDRQSE8tekh1QWFndXFON1NaYVI4em1DT2stQmZYQnRUNVZTM3p6MjBCOHRsMXdtYXZVUVd5Y19VZW44OFh3bEpIU3E1Mnk2ZUZDUDVjWF9pWmlmSEExQW5OdA?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>The New York Times</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z8" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA8" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="5" t="inlineStr"/>
-      <c r="AC8" s="5" t="inlineStr">
-        <is>
-          <t>86474f46fbfe7c4f1e4a0e19</t>
-        </is>
-      </c>
-      <c r="AD8" s="5" t="inlineStr">
-        <is>
-          <t>be5b6c35dfdad987def51679</t>
-        </is>
-      </c>
-      <c r="AE8" s="5" t="inlineStr">
-        <is>
-          <t>BALL-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="5" t="inlineStr"/>
-      <c r="AG8" s="5" t="inlineStr"/>
-      <c r="AH8" s="5" t="inlineStr"/>
-      <c r="AI8" s="5" t="inlineStr"/>
-      <c r="AJ8" s="5" t="inlineStr"/>
-      <c r="AK8" s="5" t="inlineStr"/>
-      <c r="AL8" s="5" t="inlineStr"/>
-      <c r="AM8" s="5" t="inlineStr"/>
-      <c r="AN8" s="5" t="inlineStr"/>
-      <c r="AO8" s="5" t="inlineStr"/>
-      <c r="AP8" s="5" t="inlineStr"/>
-      <c r="AQ8" s="5" t="inlineStr"/>
-      <c r="AR8" s="5" t="inlineStr"/>
-      <c r="AS8" s="5" t="inlineStr"/>
-      <c r="AT8" s="5" t="inlineStr"/>
-      <c r="AU8" s="5" t="inlineStr"/>
-      <c r="AV8" s="5" t="inlineStr"/>
-      <c r="AW8" s="5" t="inlineStr">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="5" t="inlineStr"/>
-      <c r="AY8" s="5" t="inlineStr"/>
-      <c r="AZ8" s="5" t="inlineStr"/>
-      <c r="BA8" s="5" t="inlineStr"/>
-      <c r="BB8" s="5" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>BALL</t>
         </is>
       </c>
-      <c r="BC8" s="5" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="5" t="inlineStr"/>
-      <c r="BE8" s="5" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="5" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="5" t="inlineStr">
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="5" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2253,6 +2353,10 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2303,13 +2407,17 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -2362,7 +2470,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="5" t="inlineStr"/>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>77231aa87a1e40b9899758edd7a6ee26</t>
+        </is>
+      </c>
       <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>6965d599c7b6d6b879877e52</t>
@@ -2387,7 +2499,11 @@
       <c r="AL10" s="5" t="inlineStr"/>
       <c r="AM10" s="5" t="inlineStr"/>
       <c r="AN10" s="5" t="inlineStr"/>
-      <c r="AO10" s="5" t="inlineStr"/>
+      <c r="AO10" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="5" t="inlineStr"/>
       <c r="AQ10" s="5" t="inlineStr"/>
       <c r="AR10" s="5" t="inlineStr"/>
@@ -2423,6 +2539,18 @@
         </is>
       </c>
       <c r="BH10" s="5" t="inlineStr"/>
+      <c r="BI10" s="5" t="inlineStr"/>
+      <c r="BJ10" s="5" t="inlineStr"/>
+      <c r="BK10" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2601,6 +2729,10 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2651,13 +2783,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2710,7 +2846,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>2b9ce3ac4d4846c1b2d1b1f31b92ac77</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>6619114e7c0dc2a447092bbb</t>
@@ -2735,7 +2875,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2779,6 +2923,18 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2819,7 +2975,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2829,13 +2985,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2875,7 +3035,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2888,7 +3048,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>d1c11c4f67f44d1a8332e8ea2db49d38</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>d9e14feced17617e317ccf05</t>
@@ -2913,7 +3077,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -2957,6 +3125,22 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3135,6 +3319,10 @@
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr"/>
+      <c r="BL14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3185,13 +3373,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3244,7 +3436,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>88d44ca69cfe4ba7a99ce4f775deabe7</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>9a1edc326ae7abfcc826acd0</t>
@@ -3269,7 +3465,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3305,6 +3505,18 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3345,7 +3557,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3355,13 +3567,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3401,7 +3617,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3414,7 +3630,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>755aabdb6cda4322a6616eea611d4250</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>071b9379f048e9f8391bdfbf</t>
@@ -3439,7 +3659,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3483,9 +3707,25 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH16"/>
+  <autoFilter ref="A1:BL16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3496,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3559,6 +3799,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3862,6 +4106,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3902,7 +4166,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -3912,13 +4176,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -3958,7 +4226,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -3971,7 +4239,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f9554de6cc024f99baee66bbdba239ff</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>f21f7d93c3daa8a164f5c59a</t>
@@ -3996,7 +4268,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -4040,6 +4316,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4218,6 +4510,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4396,6 +4692,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4566,710 +4866,770 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>BALL</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Ball Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Daniil Medvedev defaulted from China Open after striking spectator with ball - The Athletic</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>FBI Cuts Ties With Accenture After Missed Security Patch Linked To Data Breach</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>'-0.784</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>'-0.932</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeW81aUc3dERZMHZITHp0Zlg5OWZhb09IYUUwZTJfcTQ5Z3RYQ3BsU3dYeVJMbFZ0TDNWcEZ5d1NRVGgteXV0QW1OVDRQSE8tekh1QWFndXFON1NaYVI4em1DT2stQmZYQnRUNVZTM3p6MjBCOHRsMXdtYXZVUVd5Y19VZW44OFh3bEpIU3E1Mnk2ZUZDUDVjWF9pWmlmSEExQW5OdA?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>The New York Times</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="inlineStr"/>
-      <c r="X6" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z6" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA6" s="5" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOc3BiMWEyZUtlLWVtZDNzLUJkcjJQS0hRUzlQYWlSdnFCZElpMWsyMUpNTzlheTRXUk9POFhqUDJ1WHFxaTJQUTRWRlNGTGVnbnZVRnk1V3pORmFHbEstWDdrLUprWkxtVFZiX1BmRFFNWnBWY3lmNjM2V0xMVXdZaHhDVEdkTElhQ0FwQWQxVkdjQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="5" t="inlineStr"/>
-      <c r="AC6" s="5" t="inlineStr">
-        <is>
-          <t>86474f46fbfe7c4f1e4a0e19</t>
-        </is>
-      </c>
-      <c r="AD6" s="5" t="inlineStr">
-        <is>
-          <t>be5b6c35dfdad987def51679</t>
-        </is>
-      </c>
-      <c r="AE6" s="5" t="inlineStr">
-        <is>
-          <t>BALL-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="5" t="inlineStr"/>
-      <c r="AG6" s="5" t="inlineStr"/>
-      <c r="AH6" s="5" t="inlineStr"/>
-      <c r="AI6" s="5" t="inlineStr"/>
-      <c r="AJ6" s="5" t="inlineStr"/>
-      <c r="AK6" s="5" t="inlineStr"/>
-      <c r="AL6" s="5" t="inlineStr"/>
-      <c r="AM6" s="5" t="inlineStr"/>
-      <c r="AN6" s="5" t="inlineStr"/>
-      <c r="AO6" s="5" t="inlineStr"/>
-      <c r="AP6" s="5" t="inlineStr"/>
-      <c r="AQ6" s="5" t="inlineStr"/>
-      <c r="AR6" s="5" t="inlineStr"/>
-      <c r="AS6" s="5" t="inlineStr"/>
-      <c r="AT6" s="5" t="inlineStr"/>
-      <c r="AU6" s="5" t="inlineStr"/>
-      <c r="AV6" s="5" t="inlineStr"/>
-      <c r="AW6" s="5" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>244960a747819c4d2b54cf9b</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>e670fbcc9435d64e497e916b</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="5" t="inlineStr"/>
-      <c r="AY6" s="5" t="inlineStr"/>
-      <c r="AZ6" s="5" t="inlineStr"/>
-      <c r="BA6" s="5" t="inlineStr"/>
-      <c r="BB6" s="5" t="inlineStr">
-        <is>
-          <t>BALL</t>
-        </is>
-      </c>
-      <c r="BC6" s="5" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="5" t="inlineStr"/>
-      <c r="BE6" s="5" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="5" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="5" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="5" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FBI Cuts Ties With Accenture After Missed Security Patch Linked To Data Breach</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Private Equity Daily: Electronic Arts Bondholders Allege Default on LBO Debt</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>違約</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>'-0.537</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOb3VoOE00dXF4Z294S1V0aVR0MjVOcVptR29iZUtfVkctM2pwb2Z6ZW9XN0JFUGR1Um93MXRyM3lGcklDVWU3OTNYQnZzQUpEOXBnWmZ4djFHX1VZYW81dkdvWVpTYXBrZ1FxN0dJUjQ0M25KOEQ0LUM4WFphbVZUUmpXZXdZYXUtSWttUnU3eXlUUjYyYngxM1JiNFZ1c0VsQ0ZrOTB0UDY0OE1RT3ItV2poRFRMeWQxQ2RZY2Q4YjY?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>77231aa87a1e40b9899758edd7a6ee26</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>6965d599c7b6d6b879877e52</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>5825037cb9a0a6655e38ffce</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr">
+        <is>
+          <t>EA-DEFAULT-001</t>
+        </is>
+      </c>
+      <c r="AF7" s="5" t="inlineStr"/>
+      <c r="AG7" s="5" t="inlineStr"/>
+      <c r="AH7" s="5" t="inlineStr"/>
+      <c r="AI7" s="5" t="inlineStr"/>
+      <c r="AJ7" s="5" t="inlineStr"/>
+      <c r="AK7" s="5" t="inlineStr"/>
+      <c r="AL7" s="5" t="inlineStr"/>
+      <c r="AM7" s="5" t="inlineStr"/>
+      <c r="AN7" s="5" t="inlineStr"/>
+      <c r="AO7" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.932</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOc3BiMWEyZUtlLWVtZDNzLUJkcjJQS0hRUzlQYWlSdnFCZElpMWsyMUpNTzlheTRXUk9POFhqUDJ1WHFxaTJQUTRWRlNGTGVnbnZVRnk1V3pORmFHbEstWDdrLUprWkxtVFZiX1BmRFFNWnBWY3lmNjM2V0xMVXdZaHhDVEdkTElhQ0FwQWQxVkdjQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>244960a747819c4d2b54cf9b</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>e670fbcc9435d64e497e916b</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr">
-        <is>
-          <t>ACN-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="AP7" s="5" t="inlineStr"/>
+      <c r="AQ7" s="5" t="inlineStr"/>
+      <c r="AR7" s="5" t="inlineStr"/>
+      <c r="AS7" s="5" t="inlineStr"/>
+      <c r="AT7" s="5" t="inlineStr"/>
+      <c r="AU7" s="5" t="inlineStr"/>
+      <c r="AV7" s="5" t="inlineStr"/>
+      <c r="AW7" s="5" t="inlineStr"/>
+      <c r="AX7" s="5" t="inlineStr"/>
+      <c r="AY7" s="5" t="inlineStr"/>
+      <c r="AZ7" s="5" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="BB7" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="BC7" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BD7" s="5" t="inlineStr"/>
+      <c r="BE7" s="5" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH7" s="5" t="inlineStr"/>
+      <c r="BI7" s="5" t="inlineStr"/>
+      <c r="BJ7" s="5" t="inlineStr"/>
+      <c r="BK7" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Private Equity Daily: Electronic Arts Bondholders Allege Default on LBO Debt</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>FBI removed an Accenture contractor after a data breach exposed thousands of employees' records</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>'-0.537</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>'-0.942</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOb3VoOE00dXF4Z294S1V0aVR0MjVOcVptR29iZUtfVkctM2pwb2Z6ZW9XN0JFUGR1Um93MXRyM3lGcklDVWU3OTNYQnZzQUpEOXBnWmZ4djFHX1VZYW81dkdvWVpTYXBrZ1FxN0dJUjQ0M25KOEQ0LUM4WFphbVZUUmpXZXdZYXUtSWttUnU3eXlUUjYyYngxM1JiNFZ1c0VsQ0ZrOTB0UDY0OE1RT3ItV2poRFRMeWQxQ2RZY2Q4YjY?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z8" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA8" s="5" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE13LUFGVmlUcU93aGxwNGctbUl0eHBLODkwU1c2LWxMY0xYdW12Qi1zSlJ5QVZMbmdlX0VSamtyRlltaXJfTlQ5T2NabkRRR3JZVlFzRHN6ODF6VTRPMHg3WkNOT2tRZUdNek9MbmVodXlRME5kWlF5QUZaYw?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="5" t="inlineStr"/>
-      <c r="AC8" s="5" t="inlineStr">
-        <is>
-          <t>6965d599c7b6d6b879877e52</t>
-        </is>
-      </c>
-      <c r="AD8" s="5" t="inlineStr">
-        <is>
-          <t>5825037cb9a0a6655e38ffce</t>
-        </is>
-      </c>
-      <c r="AE8" s="5" t="inlineStr">
-        <is>
-          <t>EA-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="5" t="inlineStr"/>
-      <c r="AG8" s="5" t="inlineStr"/>
-      <c r="AH8" s="5" t="inlineStr"/>
-      <c r="AI8" s="5" t="inlineStr"/>
-      <c r="AJ8" s="5" t="inlineStr"/>
-      <c r="AK8" s="5" t="inlineStr"/>
-      <c r="AL8" s="5" t="inlineStr"/>
-      <c r="AM8" s="5" t="inlineStr"/>
-      <c r="AN8" s="5" t="inlineStr"/>
-      <c r="AO8" s="5" t="inlineStr"/>
-      <c r="AP8" s="5" t="inlineStr"/>
-      <c r="AQ8" s="5" t="inlineStr"/>
-      <c r="AR8" s="5" t="inlineStr"/>
-      <c r="AS8" s="5" t="inlineStr"/>
-      <c r="AT8" s="5" t="inlineStr"/>
-      <c r="AU8" s="5" t="inlineStr"/>
-      <c r="AV8" s="5" t="inlineStr"/>
-      <c r="AW8" s="5" t="inlineStr"/>
-      <c r="AX8" s="5" t="inlineStr"/>
-      <c r="AY8" s="5" t="inlineStr"/>
-      <c r="AZ8" s="5" t="inlineStr"/>
-      <c r="BA8" s="5" t="inlineStr"/>
-      <c r="BB8" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC8" s="5" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>d00d66f1aa9609719b56fc52</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>3c3c6443bddbd1fa0ca616a7</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="5" t="inlineStr"/>
-      <c r="BE8" s="5" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="5" t="inlineStr"/>
-      <c r="BG8" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH8" s="5" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG8" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>McDonald's Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>FBI removed an Accenture contractor after a data breach exposed thousands of employees' records</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>McDonald's hit with class action alleging AI-powered menu price-fixing</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>'-0.94</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLUw5Q0pUMS0waFlBSmFVcnpTNDNQQlByM0pOUWVtaGc3ekc3MnRVUkhPQjdlaDZxNUpIZ2R4TzFRN0ZGQ2NpOEdIR2ZNM3Nkc2FSMXZMaWN0MlctbzU4WlRSaFZvVm5jckp0N2tBcVJOb29PTDZiSGg0RURVZmhMN3h4NjVFeFYzQkM2UlREc3VPMGpjWEdMbUFKNUFlNGZaUHZB?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>2b9ce3ac4d4846c1b2d1b1f31b92ac77</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>6619114e7c0dc2a447092bbb</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>db14b425341c66039d5f451a</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>MCD-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.942</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE13LUFGVmlUcU93aGxwNGctbUl0eHBLODkwU1c2LWxMY0xYdW12Qi1zSlJ5QVZMbmdlX0VSamtyRlltaXJfTlQ5T2NabkRRR3JZVlFzRHN6ODF6VTRPMHg3WkNOT2tRZUdNek9MbmVodXlRME5kWlF5QUZaYw?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Quartz</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>d00d66f1aa9609719b56fc52</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>3c3c6443bddbd1fa0ca616a7</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>ACN-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BG9" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5284,12 +5644,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>McDonald's Corporation Common Stock</t>
+          <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5299,7 +5659,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>McDonald's hit with class action alleging AI-powered menu price-fixing</t>
+          <t>Equifax agrees to proposed $100 million settlement over credit score errors</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -5320,13 +5680,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5336,7 +5700,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>'-0.94</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -5350,12 +5714,12 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLUw5Q0pUMS0waFlBSmFVcnpTNDNQQlByM0pOUWVtaGc3ekc3MnRVUkhPQjdlaDZxNUpIZ2R4TzFRN0ZGQ2NpOEdIR2ZNM3Nkc2FSMXZMaWN0MlctbzU4WlRSaFZvVm5jckp0N2tBcVJOb29PTDZiSGg0RURVZmhMN3h4NjVFeFYzQkM2UlREc3VPMGpjWEdMbUFKNUFlNGZaUHZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQeDRDLUVwSGZuVjR6SGpfdGxjSG1oV3F0TXFKejdCdDUzN2RxdDVtUHlkbDI2dEFZNUc4UUl0RFRvRHQ0WTFrdWYza24zeHhyOEZpQ0ZDLTV4dF94Tm9wZHY5bUQySFl4c0dhbm13WGZicWVvYTFxcHVpV1JHUlBPSG40bG9EY05waHln?oc=5</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>MyNorthwest.com</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr"/>
@@ -5371,7 +5735,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -5379,20 +5743,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>d1c11c4f67f44d1a8332e8ea2db49d38</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6619114e7c0dc2a447092bbb</t>
+          <t>d9e14feced17617e317ccf05</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>db14b425341c66039d5f451a</t>
+          <t>ac8948fa6bad7dbb1290fea6</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>MCD-MAJOR_LITIGATION-001</t>
+          <t>EFX-REGULATORY_PENALTY-001</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5404,7 +5772,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -5423,7 +5795,7 @@
       <c r="BA10" s="2" t="inlineStr"/>
       <c r="BB10" s="2" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
@@ -5448,6 +5820,22 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5462,22 +5850,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Equifax, Inc. Common Stock</t>
+          <t>J.B. Hunt</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T15:00:00+08:00</t>
+          <t>2026-10-06T07:40:00+08:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Equifax agrees to proposed $100 million settlement over credit score errors</t>
+          <t>Rosen Law Firm Encourages J.B. Hunt Transport Services, Inc. Investors to Inquire About Securities Class Action Investigation - JBHT</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -5488,7 +5876,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5498,13 +5886,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5514,7 +5906,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -5528,12 +5920,12 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQeDRDLUVwSGZuVjR6SGpfdGxjSG1oV3F0TXFKejdCdDUzN2RxdDVtUHlkbDI2dEFZNUc4UUl0RFRvRHQ0WTFrdWYza24zeHhyOEZpQ0ZDLTV4dF94Tm9wZHY5bUQySFl4c0dhbm13WGZicWVvYTFxcHVpV1JHUlBPSG40bG9EY05waHln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNSVV0aWMyaE5xWEs1RzZiejdNYW9XWXRiZFRYVjkzRnJMU0NzVVctc1JlS0VhRk9zemhKNTRWdXk4WkJOd3RuV1doSG5QQUhfY003TzNTa2lxUTRBMEFRN3JleWVzOXpwUWxGbDNQNUstWG9WX2V5MHRLZUo4Z2pZbkRzaVd3WmQwcDVYTzlqMzBCb2stQUVfNXJvYXpBaGQ1RVFMOFFKandDa2VvYVFtelNKdmpUbzJFOXo5dlBMS1g2ckZDYXhlRmdleEJUNzFaVjhpV0NvMlhteVJ3VzdJbWpIdTVrMmM4SkdQYk53SjAxUzRTWDBwZ3RpZnVuZ2RONURNLWdDRUtPMW15YXByNldB?oc=5</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>MyNorthwest.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr"/>
@@ -5544,12 +5936,12 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -5557,20 +5949,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>88d44ca69cfe4ba7a99ce4f775deabe7</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>d9e14feced17617e317ccf05</t>
+          <t>9a1edc326ae7abfcc826acd0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>ac8948fa6bad7dbb1290fea6</t>
+          <t>4a8a13c5a5587bf3082d6d0f</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
+          <t>JBHT-MAJOR_LITIGATION-001</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr"/>
@@ -5582,7 +5978,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -5590,18 +5990,14 @@
       <c r="AT11" s="2" t="inlineStr"/>
       <c r="AU11" s="2" t="inlineStr"/>
       <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW11" s="2" t="inlineStr"/>
       <c r="AX11" s="2" t="inlineStr"/>
       <c r="AY11" s="2" t="inlineStr"/>
       <c r="AZ11" s="2" t="inlineStr"/>
       <c r="BA11" s="2" t="inlineStr"/>
       <c r="BB11" s="2" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="BC11" s="2" t="inlineStr">
@@ -5612,20 +6008,28 @@
       <c r="BD11" s="2" t="inlineStr"/>
       <c r="BE11" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF11" s="2" t="inlineStr"/>
       <c r="BG11" s="2" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5640,22 +6044,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt</t>
+          <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T07:40:00+08:00</t>
+          <t>2026-10-06T04:51:00+08:00</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Rosen Law Firm Encourages J.B. Hunt Transport Services, Inc. Investors to Inquire About Securities Class Action Investigation - JBHT</t>
+          <t>Equifax agrees to $100mil settlement</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -5676,13 +6080,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5692,7 +6100,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
@@ -5706,12 +6114,12 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNSVV0aWMyaE5xWEs1RzZiejdNYW9XWXRiZFRYVjkzRnJMU0NzVVctc1JlS0VhRk9zemhKNTRWdXk4WkJOd3RuV1doSG5QQUhfY003TzNTa2lxUTRBMEFRN3JleWVzOXpwUWxGbDNQNUstWG9WX2V5MHRLZUo4Z2pZbkRzaVd3WmQwcDVYTzlqMzBCb2stQUVfNXJvYXpBaGQ1RVFMOFFKandDa2VvYVFtelNKdmpUbzJFOXo5dlBMS1g2ckZDYXhlRmdleEJUNzFaVjhpV0NvMlhteVJ3VzdJbWpIdTVrMmM4SkdQYk53SjAxUzRTWDBwZ3RpZnVuZ2RONURNLWdDRUtPMW15YXByNldB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTVRZRG42M2pUejE4MnNPQW9Kc1lTWmsxNkJHNVJJNlZQeWZJUXBTbERUREk0WGFaUWJEUXdUWVJ6Q3RoT2ZLbHpma2IzWXc5UTNpeG5WaTJWbnF5VXpURkhNc2lyUE9uNlM2cERIMTliengwcmM2VEEyVnNlYW94V015SG9hY2FFclFjX0htUFdEeHJCZUlEc2ZmbUlpVVlpTE9leEtJYTJhUG9j?oc=5</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>WFAA</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr"/>
@@ -5727,7 +6135,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -5735,20 +6143,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>755aabdb6cda4322a6616eea611d4250</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9a1edc326ae7abfcc826acd0</t>
+          <t>071b9379f048e9f8391bdfbf</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>4a8a13c5a5587bf3082d6d0f</t>
+          <t>cd2d82799e42e8cce11c0c4c</t>
         </is>
       </c>
       <c r="AE12" s="2" t="inlineStr">
         <is>
-          <t>JBHT-MAJOR_LITIGATION-001</t>
+          <t>EFX-REGULATORY_PENALTY-001</t>
         </is>
       </c>
       <c r="AF12" s="2" t="inlineStr"/>
@@ -5760,7 +6172,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -5768,14 +6184,18 @@
       <c r="AT12" s="2" t="inlineStr"/>
       <c r="AU12" s="2" t="inlineStr"/>
       <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX12" s="2" t="inlineStr"/>
       <c r="AY12" s="2" t="inlineStr"/>
       <c r="AZ12" s="2" t="inlineStr"/>
       <c r="BA12" s="2" t="inlineStr"/>
       <c r="BB12" s="2" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="BC12" s="2" t="inlineStr">
@@ -5786,197 +6206,39 @@
       <c r="BD12" s="2" t="inlineStr"/>
       <c r="BE12" s="2" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF12" s="2" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG12" s="2" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06T04:51:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Equifax agrees to $100mil settlement</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.207</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTVRZRG42M2pUejE4MnNPQW9Kc1lTWmsxNkJHNVJJNlZQeWZJUXBTbERUREk0WGFaUWJEUXdUWVJ6Q3RoT2ZLbHpma2IzWXc5UTNpeG5WaTJWbnF5VXpURkhNc2lyUE9uNlM2cERIMTliengwcmM2VEEyVnNlYW94V015SG9hY2FFclFjX0htUFdEeHJCZUlEc2ZmbUlpVVlpTE9leEtJYTJhUG9j?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>WFAA</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>071b9379f048e9f8391bdfbf</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>cd2d82799e42e8cce11c0c4c</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr"/>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr"/>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
-      <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
-      <c r="AP13" s="2" t="inlineStr"/>
-      <c r="AQ13" s="2" t="inlineStr"/>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr"/>
-      <c r="AU13" s="2" t="inlineStr"/>
-      <c r="AV13" s="2" t="inlineStr"/>
-      <c r="AW13" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX13" s="2" t="inlineStr"/>
-      <c r="AY13" s="2" t="inlineStr"/>
-      <c r="AZ13" s="2" t="inlineStr"/>
-      <c r="BA13" s="2" t="inlineStr"/>
-      <c r="BB13" s="2" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC13" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="2" t="inlineStr"/>
-      <c r="BE13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG13" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5987,7 +6249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6050,6 +6312,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6351,6 +6617,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -6531,9 +6817,13 @@
       </c>
       <c r="BG2" s="4" t="inlineStr"/>
       <c r="BH2" s="4" t="inlineStr"/>
+      <c r="BI2" s="4" t="inlineStr"/>
+      <c r="BJ2" s="4" t="inlineStr"/>
+      <c r="BK2" s="4" t="inlineStr"/>
+      <c r="BL2" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH2"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6544,7 +6834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6607,6 +6897,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6910,9 +7204,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6923,7 +7237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6973,134 +7287,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -7110,46 +7424,80 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="4" t="inlineStr"/>
       <c r="Y2" s="4" t="inlineStr"/>
       <c r="Z2" s="4" t="inlineStr"/>
@@ -7158,12 +7506,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -7173,90 +7521,94 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -7266,94 +7618,94 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -7361,89 +7713,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-06.xlsx
+++ b/news_daily/2026-10-06.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -97,10 +97,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1102,28 +1102,32 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1163,7 +1167,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -1176,7 +1180,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>9f3dc435520949f1a97c5123a2990a9a</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>aa14986ff1eedf080bd3d447</t>
@@ -1201,7 +1209,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1245,1118 +1257,1210 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>2026-10-06T20:42:38+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Marathon Petroleum (MPC) Stock May Be 26% Undervalued After Diesel Export Ban Risk</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>出口管制</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.199</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNNDV2RWY3QU14cjQtbDRWeTRUMU51cG53bUtjWkprcTBtNXNUTGtzV1BvWXpGTEI3SmJLRWMzMDB0dm9mRnBfcmxyWjlETzNYSnZkeU0zY3EwRzNqWlRRRWNVai1HNTJpQVhxUVluZGFBUUhqeXk0VXoyQ2lXT1ZQUHowcHgxV3dvNWh0RUlGTHd4NUhvYWZfSi1RXzBmWkFCNnNHN0dGaXJvOVVYUkNubjhzUkUzM1E2RWUwU0lmYVZWZlMzQTIxblFHalrSAdIBQVVfeXFMUGNwbW55NEVnbEpQcUhETDZoVzJCVEVkc2xWTW9jRm1pVmVNdEROSXE4Zm5HMzh5d0dDQW4tS2otbmRkTUxlcnBKYzN3ZlhVZHA1NmZ5eHdZa2tQZVlZSHY5Y2lnYWFMWk04YWV0RG52N0lpWkpxcldSb0lDZ3gyNVhsY292UF9YMjdCRG9VY1F5bVVGSDl1dXYtemlqYlFDTEJ4U19WQXc2UnA1NDE1Ymt4bDBYTWJub0NHeEl5d2JZbzNZVzc0RV9YSmNMbTBxbjhR?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>export ban</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>09752307ec6840fb9faabe21ab78e94c</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>dfda80818bb3fc8e86c16470</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>9b4f93e7a6837315fc805449</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>MPC-EXPORT_RESTRICTION-001</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>'-0.199</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNNDV2RWY3QU14cjQtbDRWeTRUMU51cG53bUtjWkprcTBtNXNUTGtzV1BvWXpGTEI3SmJLRWMzMDB0dm9mRnBfcmxyWjlETzNYSnZkeU0zY3EwRzNqWlRRRWNVai1HNTJpQVhxUVluZGFBUUhqeXk0VXoyQ2lXT1ZQUHowcHgxV3dvNWh0RUlGTHd4NUhvYWZfSi1RXzBmWkFCNnNHN0dGaXJvOVVYUkNubjhzUkUzM1E2RWUwU0lmYVZWZlMzQTIxblFHalrSAdIBQVVfeXFMUGNwbW55NEVnbEpQcUhETDZoVzJCVEVkc2xWTW9jRm1pVmVNdEROSXE4Zm5HMzh5d0dDQW4tS2otbmRkTUxlcnBKYzN3ZlhVZHA1NmZ5eHdZa2tQZVlZSHY5Y2lnYWFMWk04YWV0RG52N0lpWkpxcldSb0lDZ3gyNVhsY292UF9YMjdCRG9VY1F5bVVGSDl1dXYtemlqYlFDTEJ4U19WQXc2UnA1NDE1Ymt4bDBYTWJub0NHeEl5d2JZbzNZVzc0RV9YSmNMbTBxbjhR?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>EXPORT_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>export ban</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>dfda80818bb3fc8e86c16470</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>9b4f93e7a6837315fc805449</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>MPC-EXPORT_RESTRICTION-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
         <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="BC4" s="3" t="inlineStr">
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BG4" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
-      <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>United Airlines Holdings</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>2026-10-06T18:49:10+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>美銀：美國聯合航空目標價下調至145美元</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2699170</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>ANALYST_DOWNGRADE</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>目標價下調</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>a8c5e2d380334a8bbd87b60504da9f74</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>0010fdfbaf45e8c61a01ba62</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>287b58f533fcde2d12e2a7bf</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>UAL-ANALYST_DOWNGRADE-001</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr"/>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2699170</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>ANALYST_DOWNGRADE</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>目標價下調</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>0010fdfbaf45e8c61a01ba62</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>287b58f533fcde2d12e2a7bf</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr">
-        <is>
-          <t>UAL-ANALYST_DOWNGRADE-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
+      <c r="BD5" s="3" t="inlineStr">
         <is>
           <t>UAL</t>
         </is>
       </c>
-      <c r="BC5" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="4" t="inlineStr">
-        <is>
-          <t>UAL</t>
-        </is>
-      </c>
-      <c r="BE5" s="4" t="inlineStr">
+      <c r="BE5" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="4" t="inlineStr">
+      <c r="BF5" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="4" t="inlineStr"/>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BG5" s="3" t="inlineStr"/>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>MSI</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Motorola Solutions, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-10-06T18:26:17+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Motorola Solutions (MSI) Stock Could Be 18% Overvalued On Cash Flow</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>'-0.63</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPNGNwaWdvVmp2TGNGRVR4MEliSXQ3eENVSHRTbk9wTjVvRDh2WGFkVkFGRUY0SDZNNWRDTmJmZ0FjTUtqTGJmbXpkdjRZdWs2NHJ0cFF4WndHaUhNS3BMVHJqTXVfSmxLN3pIT2QzeXFCNEZrajdXenJGTVpIRzRmd2ExOElxdVJjZUpjN0NzMi1qM29QSmpZSlFicUlvY2RCVEtyQ1RfTThSMmE2dmZGdy0wVEstRS1JT3NjT19aSDlXT3d5THFtQdIBzgFBVV95cUxPN3EtV0lXc0xUcC1iVnJKWS1TV3ZXbXRpWnhLbWd3eVNDenMwRk80S0VzajNGUHlYMTA2TE1FSmRXWTRiakFidlVKUXkwdXlHMnA0QTd4NkJ4ZGMyUlU1MG5oYk9EaUdpVV9nWjgyUHFMaGtzeEpwSFFuQTlIU2dZLTJYaHFHZWpibTJWWFRwSUdOSWRvNGp2U21iNDFfN0o0bWIzaTlKY3h0cFRBMDlXOTYzQ21hWl8wLUEybnJ3NVl5b0o2N1Jha3YzbjF6UQ?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>4e52639745d0bf811b87b944</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>2858902fbf02ff9051f9e395</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>MSI-VALUATION_CONCERN-001</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>MSI</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Warner Bros. Discovery</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Layoffs on the Way as Skydance Now Controls Paramount and WBD</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>裁員或人力縮減</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.951</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNRkQzU3ZQYUdicTN2QmRZZ1RlUXVJSW9DTVdZMk5HTWFMMUJZZTVWeXFlMjM5Y3RGWlNBVWR0Sm1KOVo0b2pab3h0MllVdVBid2NuMUZwMlM3VjhNME1YMXJYMFlzSE9xVXBqcklVOE9Mc1FsSDV2dTlDTFVVMTR0QTNUOWVzLVJWcnF4MEk0T1hYbFhDR2lfa0pB?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>ADWEEK</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>5db5b354264240aeb9c3cae54e073c55</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>2cd7a1f1ed9ae29448b29e85</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>5d2d61e299f760b321a3a363</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>WBD-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.951</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNRkQzU3ZQYUdicTN2QmRZZ1RlUXVJSW9DTVdZMk5HTWFMMUJZZTVWeXFlMjM5Y3RGWlNBVWR0Sm1KOVo0b2pab3h0MllVdVBid2NuMUZwMlM3VjhNME1YMXJYMFlzSE9xVXBqcklVOE9Mc1FsSDV2dTlDTFVVMTR0QTNUOWVzLVJWcnF4MEk0T1hYbFhDR2lfa0pB?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>ADWEEK</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>2cd7a1f1ed9ae29448b29e85</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>5d2d61e299f760b321a3a363</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr">
-        <is>
-          <t>WBD-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>BALL</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ball Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Daniil Medvedev defaulted from China Open after striking spectator with ball - The Athletic</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>'-0.784</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeW81aUc3dERZMHZITHp0Zlg5OWZhb09IYUUwZTJfcTQ5Z3RYQ3BsU3dYeVJMbFZ0TDNWcEZ5d1NRVGgteXV0QW1OVDRQSE8tekh1QWFndXFON1NaYVI4em1DT2stQmZYQnRUNVZTM3p6MjBCOHRsMXdtYXZVUVd5Y19VZW44OFh3bEpIU3E1Mnk2ZUZDUDVjWF9pWmlmSEExQW5OdA?oc=5</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="V8" s="3" t="inlineStr">
         <is>
           <t>The New York Times</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t>FINANCIAL</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>eab9231675914654aee8756a674f46c0</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="inlineStr">
+      <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>86474f46fbfe7c4f1e4a0e19</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AD8" s="3" t="inlineStr">
         <is>
           <t>be5b6c35dfdad987def51679</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AE8" s="3" t="inlineStr">
         <is>
           <t>BALL-DEFAULT-001</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr">
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
         <is>
           <t>BALL</t>
         </is>
       </c>
-      <c r="BC8" s="4" t="inlineStr">
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="4" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="4" t="inlineStr">
+      <c r="BG8" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr">
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL8" s="4" t="inlineStr">
+      <c r="BL8" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>ACN</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>FBI Cuts Ties With Accenture After Missed Security Patch Linked To Data Breach</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>資料外洩</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>'-0.932</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOc3BiMWEyZUtlLWVtZDNzLUJkcjJQS0hRUzlQYWlSdnFCZElpMWsyMUpNTzlheTRXUk9POFhqUDJ1WHFxaTJQUTRWRlNGTGVnbnZVRnk1V3pORmFHbEstWDdrLUprWkxtVFZiX1BmRFFNWnBWY3lmNjM2V0xMVXdZaHhDVEdkTElhQ0FwQWQxVkdjQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>aa0b0826335f44019780350f86d66a0d</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>244960a747819c4d2b54cf9b</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>e670fbcc9435d64e497e916b</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.932</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOc3BiMWEyZUtlLWVtZDNzLUJkcjJQS0hRUzlQYWlSdnFCZElpMWsyMUpNTzlheTRXUk9POFhqUDJ1WHFxaTJQUTRWRlNGTGVnbnZVRnk1V3pORmFHbEstWDdrLUprWkxtVFZiX1BmRFFNWnBWY3lmNjM2V0xMVXdZaHhDVEdkTElhQ0FwQWQxVkdjQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>244960a747819c4d2b54cf9b</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>e670fbcc9435d64e497e916b</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>ACN-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
         <is>
           <t>ACN</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr">
+      <c r="BF9" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2553,186 +2657,206 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>ACN</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>FBI removed an Accenture contractor after a data breach exposed thousands of employees' records</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>資料外洩</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>'-0.942</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE13LUFGVmlUcU93aGxwNGctbUl0eHBLODkwU1c2LWxMY0xYdW12Qi1zSlJ5QVZMbmdlX0VSamtyRlltaXJfTlQ5T2NabkRRR3JZVlFzRHN6ODF6VTRPMHg3WkNOT2tRZUdNek9MbmVodXlRME5kWlF5QUZaYw?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>470ca7b108cb4d6aa54c581764c778ac</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>d00d66f1aa9609719b56fc52</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>3c3c6443bddbd1fa0ca616a7</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.942</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE13LUFGVmlUcU93aGxwNGctbUl0eHBLODkwU1c2LWxMY0xYdW12Qi1zSlJ5QVZMbmdlX0VSamtyRlltaXJfTlQ5T2NabkRRR3JZVlFzRHN6ODF6VTRPMHg3WkNOT2tRZUdNek9MbmVodXlRME5kWlF5QUZaYw?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Quartz</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>d00d66f1aa9609719b56fc52</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>3c3c6443bddbd1fa0ca616a7</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr">
-        <is>
-          <t>ACN-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
         <is>
           <t>ACN</t>
         </is>
       </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3143,186 +3267,186 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>PTC</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>PTC Inc.</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>2026-10-06T10:40:34+08:00</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>法國施耐德電氣股價重挫10%，將以226億美元收購美國軟件公司PTC</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr">
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>https://tw.tradingview.com/symbols/NASDAQ-PTC/news/</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr">
+      <c r="V14" s="3" t="inlineStr">
         <is>
           <t>TradingView</t>
         </is>
       </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y14" s="4" t="inlineStr">
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>重挫</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>44dfacedfb29986f7784a7e2</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AD14" s="3" t="inlineStr">
         <is>
           <t>2d09963d494e9df917451a79</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>PTC-PRICE_MOVEMENT-001</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr"/>
+      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="inlineStr"/>
+      <c r="AV14" s="3" t="inlineStr"/>
+      <c r="AW14" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
+      <c r="AX14" s="3" t="inlineStr"/>
+      <c r="AY14" s="3" t="inlineStr"/>
+      <c r="AZ14" s="3" t="inlineStr"/>
+      <c r="BA14" s="3" t="inlineStr"/>
+      <c r="BB14" s="3" t="inlineStr">
         <is>
           <t>PTC</t>
         </is>
       </c>
-      <c r="BC14" s="4" t="inlineStr">
+      <c r="BC14" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
+      <c r="BD14" s="3" t="inlineStr"/>
+      <c r="BE14" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF14" s="4" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG14" s="4" t="inlineStr">
+      <c r="BG14" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="4" t="inlineStr"/>
-      <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr"/>
-      <c r="BK14" s="4" t="inlineStr"/>
-      <c r="BL14" s="4" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3736,7 +3860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL12"/>
+  <dimension ref="A1:BL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4334,1100 +4458,1200 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-06T23:04:04+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Uber strikes $2.3B deal for ezCater as freight unit adds supply chain exec</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T20:42:38+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum (MPC) Stock May Be 26% Undervalued After Diesel Export Ban Risk</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.199</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNNDV2RWY3QU14cjQtbDRWeTRUMU51cG53bUtjWkprcTBtNXNUTGtzV1BvWXpGTEI3SmJLRWMzMDB0dm9mRnBfcmxyWjlETzNYSnZkeU0zY3EwRzNqWlRRRWNVai1HNTJpQVhxUVluZGFBUUhqeXk0VXoyQ2lXT1ZQUHowcHgxV3dvNWh0RUlGTHd4NUhvYWZfSi1RXzBmWkFCNnNHN0dGaXJvOVVYUkNubjhzUkUzM1E2RWUwU0lmYVZWZlMzQTIxblFHalrSAdIBQVVfeXFMUGNwbW55NEVnbEpQcUhETDZoVzJCVEVkc2xWTW9jRm1pVmVNdEROSXE4Zm5HMzh5d0dDQW4tS2otbmRkTUxlcnBKYzN3ZlhVZHA1NmZ5eHdZa2tQZVlZSHY5Y2lnYWFMWk04YWV0RG52N0lpWkpxcldSb0lDZ3gyNVhsY292UF9YMjdCRG9VY1F5bVVGSDl1dXYtemlqYlFDTEJ4U19WQXc2UnA1NDE1Ymt4bDBYTWJub0NHeEl5d2JZbzNZVzc0RV9YSmNMbTBxbjhR?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>export ban</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>09752307ec6840fb9faabe21ab78e94c</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>dfda80818bb3fc8e86c16470</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>9b4f93e7a6837315fc805449</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>MPC-EXPORT_RESTRICTION-001</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.865</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOdi03VVpYeFRCRGk0d1RxSVNTRnVwUXZGY0FoZGpONm1Da3pOVjRCU2hwcF9JMDRRX3pibDF6eWlncWQ0eHF2ZFdSV0loTk9NM082UFR1OFAwOFp4aGc5Z2ZNSnEzQXBOM0hwcW1IcVFoZUdUd2FPeXVLbjNUUzN3ZWpvbGZCWncta1FOYWtmTUEtaTBlNkR2bzVkNDZiendNLWJMYUt2RWJqNnM?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>FreightWaves</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>aa14986ff1eedf080bd3d447</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>fbdeb91112aa5f8f0c17528c</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>UBER-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-06T20:42:38+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum (MPC) Stock May Be 26% Undervalued After Diesel Export Ban Risk</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Layoffs on the Way as Skydance Now Controls Paramount and WBD</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>出口管制</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.951</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNRkQzU3ZQYUdicTN2QmRZZ1RlUXVJSW9DTVdZMk5HTWFMMUJZZTVWeXFlMjM5Y3RGWlNBVWR0Sm1KOVo0b2pab3h0MllVdVBid2NuMUZwMlM3VjhNME1YMXJYMFlzSE9xVXBqcklVOE9Mc1FsSDV2dTlDTFVVMTR0QTNUOWVzLVJWcnF4MEk0T1hYbFhDR2lfa0pB?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>ADWEEK</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>5db5b354264240aeb9c3cae54e073c55</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>2cd7a1f1ed9ae29448b29e85</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>5d2d61e299f760b321a3a363</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>WBD-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>'-0.199</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNNDV2RWY3QU14cjQtbDRWeTRUMU51cG53bUtjWkprcTBtNXNUTGtzV1BvWXpGTEI3SmJLRWMzMDB0dm9mRnBfcmxyWjlETzNYSnZkeU0zY3EwRzNqWlRRRWNVai1HNTJpQVhxUVluZGFBUUhqeXk0VXoyQ2lXT1ZQUHowcHgxV3dvNWh0RUlGTHd4NUhvYWZfSi1RXzBmWkFCNnNHN0dGaXJvOVVYUkNubjhzUkUzM1E2RWUwU0lmYVZWZlMzQTIxblFHalrSAdIBQVVfeXFMUGNwbW55NEVnbEpQcUhETDZoVzJCVEVkc2xWTW9jRm1pVmVNdEROSXE4Zm5HMzh5d0dDQW4tS2otbmRkTUxlcnBKYzN3ZlhVZHA1NmZ5eHdZa2tQZVlZSHY5Y2lnYWFMWk04YWV0RG52N0lpWkpxcldSb0lDZ3gyNVhsY292UF9YMjdCRG9VY1F5bVVGSDl1dXYtemlqYlFDTEJ4U19WQXc2UnA1NDE1Ymt4bDBYTWJub0NHeEl5d2JZbzNZVzc0RV9YSmNMbTBxbjhR?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>EXPORT_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>export ban</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>dfda80818bb3fc8e86c16470</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>9b4f93e7a6837315fc805449</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>MPC-EXPORT_RESTRICTION-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr"/>
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
-      <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr"/>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Layoffs on the Way as Skydance Now Controls Paramount and WBD</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>FBI Cuts Ties With Accenture After Missed Security Patch Linked To Data Breach</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.932</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOc3BiMWEyZUtlLWVtZDNzLUJkcjJQS0hRUzlQYWlSdnFCZElpMWsyMUpNTzlheTRXUk9POFhqUDJ1WHFxaTJQUTRWRlNGTGVnbnZVRnk1V3pORmFHbEstWDdrLUprWkxtVFZiX1BmRFFNWnBWY3lmNjM2V0xMVXdZaHhDVEdkTElhQ0FwQWQxVkdjQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>aa0b0826335f44019780350f86d66a0d</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>244960a747819c4d2b54cf9b</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>e670fbcc9435d64e497e916b</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.951</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNRkQzU3ZQYUdicTN2QmRZZ1RlUXVJSW9DTVdZMk5HTWFMMUJZZTVWeXFlMjM5Y3RGWlNBVWR0Sm1KOVo0b2pab3h0MllVdVBid2NuMUZwMlM3VjhNME1YMXJYMFlzSE9xVXBqcklVOE9Mc1FsSDV2dTlDTFVVMTR0QTNUOWVzLVJWcnF4MEk0T1hYbFhDR2lfa0pB?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>ADWEEK</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>2cd7a1f1ed9ae29448b29e85</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>5d2d61e299f760b321a3a363</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>WBD-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr"/>
-      <c r="BG5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>FBI Cuts Ties With Accenture After Missed Security Patch Linked To Data Breach</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Private Equity Daily: Electronic Arts Bondholders Allege Default on LBO Debt</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>違約</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>'-0.537</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOb3VoOE00dXF4Z294S1V0aVR0MjVOcVptR29iZUtfVkctM2pwb2Z6ZW9XN0JFUGR1Um93MXRyM3lGcklDVWU3OTNYQnZzQUpEOXBnWmZ4djFHX1VZYW81dkdvWVpTYXBrZ1FxN0dJUjQ0M25KOEQ0LUM4WFphbVZUUmpXZXdZYXUtSWttUnU3eXlUUjYyYngxM1JiNFZ1c0VsQ0ZrOTB0UDY0OE1RT3ItV2poRFRMeWQxQ2RZY2Q4YjY?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>77231aa87a1e40b9899758edd7a6ee26</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>6965d599c7b6d6b879877e52</t>
+        </is>
+      </c>
+      <c r="AD6" s="5" t="inlineStr">
+        <is>
+          <t>5825037cb9a0a6655e38ffce</t>
+        </is>
+      </c>
+      <c r="AE6" s="5" t="inlineStr">
+        <is>
+          <t>EA-DEFAULT-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="5" t="inlineStr"/>
+      <c r="AG6" s="5" t="inlineStr"/>
+      <c r="AH6" s="5" t="inlineStr"/>
+      <c r="AI6" s="5" t="inlineStr"/>
+      <c r="AJ6" s="5" t="inlineStr"/>
+      <c r="AK6" s="5" t="inlineStr"/>
+      <c r="AL6" s="5" t="inlineStr"/>
+      <c r="AM6" s="5" t="inlineStr"/>
+      <c r="AN6" s="5" t="inlineStr"/>
+      <c r="AO6" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.932</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOc3BiMWEyZUtlLWVtZDNzLUJkcjJQS0hRUzlQYWlSdnFCZElpMWsyMUpNTzlheTRXUk9POFhqUDJ1WHFxaTJQUTRWRlNGTGVnbnZVRnk1V3pORmFHbEstWDdrLUprWkxtVFZiX1BmRFFNWnBWY3lmNjM2V0xMVXdZaHhDVEdkTElhQ0FwQWQxVkdjQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>244960a747819c4d2b54cf9b</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>e670fbcc9435d64e497e916b</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>ACN-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="AP6" s="5" t="inlineStr"/>
+      <c r="AQ6" s="5" t="inlineStr"/>
+      <c r="AR6" s="5" t="inlineStr"/>
+      <c r="AS6" s="5" t="inlineStr"/>
+      <c r="AT6" s="5" t="inlineStr"/>
+      <c r="AU6" s="5" t="inlineStr"/>
+      <c r="AV6" s="5" t="inlineStr"/>
+      <c r="AW6" s="5" t="inlineStr"/>
+      <c r="AX6" s="5" t="inlineStr"/>
+      <c r="AY6" s="5" t="inlineStr"/>
+      <c r="AZ6" s="5" t="inlineStr"/>
+      <c r="BA6" s="5" t="inlineStr"/>
+      <c r="BB6" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="BC6" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BD6" s="5" t="inlineStr"/>
+      <c r="BE6" s="5" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="5" t="inlineStr"/>
+      <c r="BG6" s="5" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH6" s="5" t="inlineStr"/>
+      <c r="BI6" s="5" t="inlineStr"/>
+      <c r="BJ6" s="5" t="inlineStr"/>
+      <c r="BK6" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Private Equity Daily: Electronic Arts Bondholders Allege Default on LBO Debt</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>FBI removed an Accenture contractor after a data breach exposed thousands of employees' records</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>'-0.537</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.942</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOb3VoOE00dXF4Z294S1V0aVR0MjVOcVptR29iZUtfVkctM2pwb2Z6ZW9XN0JFUGR1Um93MXRyM3lGcklDVWU3OTNYQnZzQUpEOXBnWmZ4djFHX1VZYW81dkdvWVpTYXBrZ1FxN0dJUjQ0M25KOEQ0LUM4WFphbVZUUmpXZXdZYXUtSWttUnU3eXlUUjYyYngxM1JiNFZ1c0VsQ0ZrOTB0UDY0OE1RT3ItV2poRFRMeWQxQ2RZY2Q4YjY?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="inlineStr"/>
-      <c r="X7" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z7" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE13LUFGVmlUcU93aGxwNGctbUl0eHBLODkwU1c2LWxMY0xYdW12Qi1zSlJ5QVZMbmdlX0VSamtyRlltaXJfTlQ5T2NabkRRR3JZVlFzRHN6ODF6VTRPMHg3WkNOT2tRZUdNek9MbmVodXlRME5kWlF5QUZaYw?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
-        <is>
-          <t>77231aa87a1e40b9899758edd7a6ee26</t>
-        </is>
-      </c>
-      <c r="AC7" s="5" t="inlineStr">
-        <is>
-          <t>6965d599c7b6d6b879877e52</t>
-        </is>
-      </c>
-      <c r="AD7" s="5" t="inlineStr">
-        <is>
-          <t>5825037cb9a0a6655e38ffce</t>
-        </is>
-      </c>
-      <c r="AE7" s="5" t="inlineStr">
-        <is>
-          <t>EA-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="5" t="inlineStr"/>
-      <c r="AG7" s="5" t="inlineStr"/>
-      <c r="AH7" s="5" t="inlineStr"/>
-      <c r="AI7" s="5" t="inlineStr"/>
-      <c r="AJ7" s="5" t="inlineStr"/>
-      <c r="AK7" s="5" t="inlineStr"/>
-      <c r="AL7" s="5" t="inlineStr"/>
-      <c r="AM7" s="5" t="inlineStr"/>
-      <c r="AN7" s="5" t="inlineStr"/>
-      <c r="AO7" s="5" t="inlineStr">
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>470ca7b108cb4d6aa54c581764c778ac</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>d00d66f1aa9609719b56fc52</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>3c3c6443bddbd1fa0ca616a7</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP7" s="5" t="inlineStr"/>
-      <c r="AQ7" s="5" t="inlineStr"/>
-      <c r="AR7" s="5" t="inlineStr"/>
-      <c r="AS7" s="5" t="inlineStr"/>
-      <c r="AT7" s="5" t="inlineStr"/>
-      <c r="AU7" s="5" t="inlineStr"/>
-      <c r="AV7" s="5" t="inlineStr"/>
-      <c r="AW7" s="5" t="inlineStr"/>
-      <c r="AX7" s="5" t="inlineStr"/>
-      <c r="AY7" s="5" t="inlineStr"/>
-      <c r="AZ7" s="5" t="inlineStr"/>
-      <c r="BA7" s="5" t="inlineStr"/>
-      <c r="BB7" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC7" s="5" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="5" t="inlineStr"/>
-      <c r="BE7" s="5" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="5" t="inlineStr"/>
-      <c r="BG7" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="5" t="inlineStr"/>
-      <c r="BI7" s="5" t="inlineStr"/>
-      <c r="BJ7" s="5" t="inlineStr"/>
-      <c r="BK7" s="5" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL7" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>McDonald's Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-06T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>FBI removed an Accenture contractor after a data breach exposed thousands of employees' records</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>McDonald's hit with class action alleging AI-powered menu price-fixing</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>'-0.94</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLUw5Q0pUMS0waFlBSmFVcnpTNDNQQlByM0pOUWVtaGc3ekc3MnRVUkhPQjdlaDZxNUpIZ2R4TzFRN0ZGQ2NpOEdIR2ZNM3Nkc2FSMXZMaWN0MlctbzU4WlRSaFZvVm5jckp0N2tBcVJOb29PTDZiSGg0RURVZmhMN3h4NjVFeFYzQkM2UlREc3VPMGpjWEdMbUFKNUFlNGZaUHZB?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>2b9ce3ac4d4846c1b2d1b1f31b92ac77</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>6619114e7c0dc2a447092bbb</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>db14b425341c66039d5f451a</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>MCD-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>'-0.942</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE13LUFGVmlUcU93aGxwNGctbUl0eHBLODkwU1c2LWxMY0xYdW12Qi1zSlJ5QVZMbmdlX0VSamtyRlltaXJfTlQ5T2NabkRRR3JZVlFzRHN6ODF6VTRPMHg3WkNOT2tRZUdNek9MbmVodXlRME5kWlF5QUZaYw?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Quartz</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>d00d66f1aa9609719b56fc52</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>3c3c6443bddbd1fa0ca616a7</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr">
-        <is>
-          <t>ACN-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5442,12 +5666,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>McDonald's Corporation Common Stock</t>
+          <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5457,7 +5681,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>McDonald's hit with class action alleging AI-powered menu price-fixing</t>
+          <t>Equifax agrees to proposed $100 million settlement over credit score errors</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -5498,7 +5722,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>'-0.94</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -5512,12 +5736,12 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLUw5Q0pUMS0waFlBSmFVcnpTNDNQQlByM0pOUWVtaGc3ekc3MnRVUkhPQjdlaDZxNUpIZ2R4TzFRN0ZGQ2NpOEdIR2ZNM3Nkc2FSMXZMaWN0MlctbzU4WlRSaFZvVm5jckp0N2tBcVJOb29PTDZiSGg0RURVZmhMN3h4NjVFeFYzQkM2UlREc3VPMGpjWEdMbUFKNUFlNGZaUHZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQeDRDLUVwSGZuVjR6SGpfdGxjSG1oV3F0TXFKejdCdDUzN2RxdDVtUHlkbDI2dEFZNUc4UUl0RFRvRHQ0WTFrdWYza24zeHhyOEZpQ0ZDLTV4dF94Tm9wZHY5bUQySFl4c0dhbm13WGZicWVvYTFxcHVpV1JHUlBPSG40bG9EY05waHln?oc=5</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>MyNorthwest.com</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
@@ -5533,7 +5757,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -5543,22 +5767,22 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>2b9ce3ac4d4846c1b2d1b1f31b92ac77</t>
+          <t>d1c11c4f67f44d1a8332e8ea2db49d38</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6619114e7c0dc2a447092bbb</t>
+          <t>d9e14feced17617e317ccf05</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>db14b425341c66039d5f451a</t>
+          <t>ac8948fa6bad7dbb1290fea6</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>MCD-MAJOR_LITIGATION-001</t>
+          <t>EFX-REGULATORY_PENALTY-001</t>
         </is>
       </c>
       <c r="AF9" s="2" t="inlineStr"/>
@@ -5593,7 +5817,7 @@
       <c r="BA9" s="2" t="inlineStr"/>
       <c r="BB9" s="2" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="BC9" s="2" t="inlineStr">
@@ -5618,7 +5842,11 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
       <c r="BK9" s="2" t="inlineStr">
         <is>
@@ -5644,22 +5872,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Equifax, Inc. Common Stock</t>
+          <t>J.B. Hunt</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T15:00:00+08:00</t>
+          <t>2026-10-06T07:40:00+08:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Equifax agrees to proposed $100 million settlement over credit score errors</t>
+          <t>Rosen Law Firm Encourages J.B. Hunt Transport Services, Inc. Investors to Inquire About Securities Class Action Investigation - JBHT</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -5700,7 +5928,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -5714,12 +5942,12 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQeDRDLUVwSGZuVjR6SGpfdGxjSG1oV3F0TXFKejdCdDUzN2RxdDVtUHlkbDI2dEFZNUc4UUl0RFRvRHQ0WTFrdWYza24zeHhyOEZpQ0ZDLTV4dF94Tm9wZHY5bUQySFl4c0dhbm13WGZicWVvYTFxcHVpV1JHUlBPSG40bG9EY05waHln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNSVV0aWMyaE5xWEs1RzZiejdNYW9XWXRiZFRYVjkzRnJMU0NzVVctc1JlS0VhRk9zemhKNTRWdXk4WkJOd3RuV1doSG5QQUhfY003TzNTa2lxUTRBMEFRN3JleWVzOXpwUWxGbDNQNUstWG9WX2V5MHRLZUo4Z2pZbkRzaVd3WmQwcDVYTzlqMzBCb2stQUVfNXJvYXpBaGQ1RVFMOFFKandDa2VvYVFtelNKdmpUbzJFOXo5dlBMS1g2ckZDYXhlRmdleEJUNzFaVjhpV0NvMlhteVJ3VzdJbWpIdTVrMmM4SkdQYk53SjAxUzRTWDBwZ3RpZnVuZ2RONURNLWdDRUtPMW15YXByNldB?oc=5</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>MyNorthwest.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr"/>
@@ -5735,7 +5963,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -5745,22 +5973,22 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>d1c11c4f67f44d1a8332e8ea2db49d38</t>
+          <t>88d44ca69cfe4ba7a99ce4f775deabe7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>d9e14feced17617e317ccf05</t>
+          <t>9a1edc326ae7abfcc826acd0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>ac8948fa6bad7dbb1290fea6</t>
+          <t>4a8a13c5a5587bf3082d6d0f</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
+          <t>JBHT-MAJOR_LITIGATION-001</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5784,18 +6012,14 @@
       <c r="AT10" s="2" t="inlineStr"/>
       <c r="AU10" s="2" t="inlineStr"/>
       <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW10" s="2" t="inlineStr"/>
       <c r="AX10" s="2" t="inlineStr"/>
       <c r="AY10" s="2" t="inlineStr"/>
       <c r="AZ10" s="2" t="inlineStr"/>
       <c r="BA10" s="2" t="inlineStr"/>
       <c r="BB10" s="2" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
@@ -5806,25 +6030,17 @@
       <c r="BD10" s="2" t="inlineStr"/>
       <c r="BE10" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF10" s="2" t="inlineStr"/>
       <c r="BG10" s="2" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
+      <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
       <c r="BK10" s="2" t="inlineStr">
         <is>
@@ -5850,22 +6066,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt</t>
+          <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T07:40:00+08:00</t>
+          <t>2026-10-06T04:51:00+08:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Rosen Law Firm Encourages J.B. Hunt Transport Services, Inc. Investors to Inquire About Securities Class Action Investigation - JBHT</t>
+          <t>Equifax agrees to $100mil settlement</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -5906,7 +6122,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -5920,12 +6136,12 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNSVV0aWMyaE5xWEs1RzZiejdNYW9XWXRiZFRYVjkzRnJMU0NzVVctc1JlS0VhRk9zemhKNTRWdXk4WkJOd3RuV1doSG5QQUhfY003TzNTa2lxUTRBMEFRN3JleWVzOXpwUWxGbDNQNUstWG9WX2V5MHRLZUo4Z2pZbkRzaVd3WmQwcDVYTzlqMzBCb2stQUVfNXJvYXpBaGQ1RVFMOFFKandDa2VvYVFtelNKdmpUbzJFOXo5dlBMS1g2ckZDYXhlRmdleEJUNzFaVjhpV0NvMlhteVJ3VzdJbWpIdTVrMmM4SkdQYk53SjAxUzRTWDBwZ3RpZnVuZ2RONURNLWdDRUtPMW15YXByNldB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTVRZRG42M2pUejE4MnNPQW9Kc1lTWmsxNkJHNVJJNlZQeWZJUXBTbERUREk0WGFaUWJEUXdUWVJ6Q3RoT2ZLbHpma2IzWXc5UTNpeG5WaTJWbnF5VXpURkhNc2lyUE9uNlM2cERIMTliengwcmM2VEEyVnNlYW94V015SG9hY2FFclFjX0htUFdEeHJCZUlEc2ZmbUlpVVlpTE9leEtJYTJhUG9j?oc=5</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>WFAA</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr"/>
@@ -5941,7 +6157,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -5951,22 +6167,22 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88d44ca69cfe4ba7a99ce4f775deabe7</t>
+          <t>755aabdb6cda4322a6616eea611d4250</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9a1edc326ae7abfcc826acd0</t>
+          <t>071b9379f048e9f8391bdfbf</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>4a8a13c5a5587bf3082d6d0f</t>
+          <t>cd2d82799e42e8cce11c0c4c</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>JBHT-MAJOR_LITIGATION-001</t>
+          <t>EFX-REGULATORY_PENALTY-001</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr"/>
@@ -5990,14 +6206,18 @@
       <c r="AT11" s="2" t="inlineStr"/>
       <c r="AU11" s="2" t="inlineStr"/>
       <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX11" s="2" t="inlineStr"/>
       <c r="AY11" s="2" t="inlineStr"/>
       <c r="AZ11" s="2" t="inlineStr"/>
       <c r="BA11" s="2" t="inlineStr"/>
       <c r="BB11" s="2" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="BC11" s="2" t="inlineStr">
@@ -6008,17 +6228,25 @@
       <c r="BD11" s="2" t="inlineStr"/>
       <c r="BE11" s="2" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="2" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG11" s="2" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
       <c r="BK11" s="2" t="inlineStr">
         <is>
@@ -6031,214 +6259,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06T04:51:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Equifax agrees to $100mil settlement</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0.207</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTVRZRG42M2pUejE4MnNPQW9Kc1lTWmsxNkJHNVJJNlZQeWZJUXBTbERUREk0WGFaUWJEUXdUWVJ6Q3RoT2ZLbHpma2IzWXc5UTNpeG5WaTJWbnF5VXpURkhNc2lyUE9uNlM2cERIMTliengwcmM2VEEyVnNlYW94V015SG9hY2FFclFjX0htUFdEeHJCZUlEc2ZmbUlpVVlpTE9leEtJYTJhUG9j?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>WFAA</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>755aabdb6cda4322a6616eea611d4250</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>071b9379f048e9f8391bdfbf</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>cd2d82799e42e8cce11c0c4c</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC12" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL12"/>
+  <autoFilter ref="A1:BL11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6249,7 +6271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6640,190 +6662,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>United Airlines Holdings</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06T18:49:10+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>美銀：美國聯合航空目標價下調至145美元</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>分析師降評</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2699170</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y2" s="4" t="inlineStr">
-        <is>
-          <t>ANALYST_DOWNGRADE</t>
-        </is>
-      </c>
-      <c r="Z2" s="4" t="inlineStr">
-        <is>
-          <t>目標價下調</t>
-        </is>
-      </c>
-      <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="inlineStr">
-        <is>
-          <t>0010fdfbaf45e8c61a01ba62</t>
-        </is>
-      </c>
-      <c r="AD2" s="4" t="inlineStr">
-        <is>
-          <t>287b58f533fcde2d12e2a7bf</t>
-        </is>
-      </c>
-      <c r="AE2" s="4" t="inlineStr">
-        <is>
-          <t>UAL-ANALYST_DOWNGRADE-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="4" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
-      <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="inlineStr"/>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="inlineStr"/>
-      <c r="AL2" s="4" t="inlineStr"/>
-      <c r="AM2" s="4" t="inlineStr"/>
-      <c r="AN2" s="4" t="inlineStr"/>
-      <c r="AO2" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="4" t="inlineStr"/>
-      <c r="AQ2" s="4" t="inlineStr"/>
-      <c r="AR2" s="4" t="inlineStr"/>
-      <c r="AS2" s="4" t="inlineStr"/>
-      <c r="AT2" s="4" t="inlineStr"/>
-      <c r="AU2" s="4" t="inlineStr"/>
-      <c r="AV2" s="4" t="inlineStr"/>
-      <c r="AW2" s="4" t="inlineStr"/>
-      <c r="AX2" s="4" t="inlineStr"/>
-      <c r="AY2" s="4" t="inlineStr"/>
-      <c r="AZ2" s="4" t="inlineStr"/>
-      <c r="BA2" s="4" t="inlineStr"/>
-      <c r="BB2" s="4" t="inlineStr">
-        <is>
-          <t>UAL</t>
-        </is>
-      </c>
-      <c r="BC2" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="4" t="inlineStr">
-        <is>
-          <t>UAL</t>
-        </is>
-      </c>
-      <c r="BE2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="4" t="inlineStr"/>
-      <c r="BH2" s="4" t="inlineStr"/>
-      <c r="BI2" s="4" t="inlineStr"/>
-      <c r="BJ2" s="4" t="inlineStr"/>
-      <c r="BK2" s="4" t="inlineStr"/>
-      <c r="BL2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7407,645 +7247,645 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>daily-2026-10-26</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H2" s="4" t="b">
+      <c r="H2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T08:23:38.366332+08:00</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T08:40:53.776257+08:00</t>
         </is>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="3" t="n">
         <v>1926</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="Q2" s="3" t="n">
         <v>1976</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="3" t="n">
         <v>1961</v>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
         </is>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="3" t="n">
         <v>1961</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>daily-2026-10-25</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="H3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>2026-10-25T08:23:17.137147+08:00</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2026-10-25T08:40:12.120180+08:00</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="3" t="n">
         <v>2032</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="Q3" s="3" t="n">
         <v>2089</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="3" t="n">
         <v>2067</v>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
         </is>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="3" t="n">
         <v>2067</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W3" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>daily-2026-10-24</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H4" s="4" t="b">
+      <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T12:44:09.884829+08:00</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T13:04:34.984103+08:00</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="3" t="n">
         <v>3760</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="Q4" s="3" t="n">
         <v>3802</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="3" t="n">
         <v>3825</v>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
         </is>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="3" t="n">
         <v>3793</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="W4" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>ticker-audit</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296780+08:00</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296790+08:00</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="n">
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="n">
         <v>1691</v>
       </c>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="n">
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="Y5" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>2026-10-22T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="b">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:34.299718+08:00</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:32:11.776786+08:00</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="W6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H7" s="4" t="b">
+      <c r="H7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="Q7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="R7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="V7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="W7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H8" s="4" t="b">
+      <c r="H8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="Q8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="V8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA8"/>

--- a/news_daily/2026-10-06.xlsx
+++ b/news_daily/2026-10-06.xlsx
@@ -1712,28 +1712,32 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1773,7 +1777,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1786,7 +1790,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>9d7bc153277d48998f420e8507223632</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>4e52639745d0bf811b87b944</t>
@@ -1811,7 +1819,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1855,10 +1867,22 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -3300,28 +3324,32 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3361,7 +3389,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -3374,7 +3402,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>0a0e3269c38747d8bccc522a9cc03d13</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>44dfacedfb29986f7784a7e2</t>
@@ -3399,7 +3431,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3443,10 +3479,22 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
